--- a/참고자료/재근메모.xlsx
+++ b/참고자료/재근메모.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mbc\MBCA\00_Remind\참고자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5518BC36-716B-4D39-957A-B890E5747F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3333411-2FE3-4D52-8C49-83E38388D8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10860" yWindow="2475" windowWidth="13935" windowHeight="9300" xr2:uid="{75E1FFC0-A2FE-4E8D-84FB-657049B41931}"/>
+    <workbookView xWindow="12660" yWindow="990" windowWidth="13935" windowHeight="14400" xr2:uid="{75E1FFC0-A2FE-4E8D-84FB-657049B41931}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Ai 변화</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -60,6 +61,30 @@
   </si>
   <si>
     <t xml:space="preserve">view -&gt; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머신러닝 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구글드라이브에 코랩 없을시, 구글에 구글코랩 검색 ㄱ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Or</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구글메뉴에서 기타 앱 제품 찾기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add python.exe to PATH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파이썬 설치시 체크하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -424,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C522516C-CF92-4DAF-812F-1C05FE71279D}">
-  <dimension ref="B2:C13"/>
+  <dimension ref="B2:C22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.3">
@@ -437,30 +462,60 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C9" t="s">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B12">
         <v>2</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -468,4 +523,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C46D7E57-29F3-49EE-8265-247E811E8E62}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/참고자료/재근메모.xlsx
+++ b/참고자료/재근메모.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mbc\MBCA\00_Remind\참고자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3333411-2FE3-4D52-8C49-83E38388D8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E9E618-D8FC-4348-8487-CB3CEADF4B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12660" yWindow="990" windowWidth="13935" windowHeight="14400" xr2:uid="{75E1FFC0-A2FE-4E8D-84FB-657049B41931}"/>
+    <workbookView xWindow="1995" yWindow="915" windowWidth="19875" windowHeight="14400" xr2:uid="{75E1FFC0-A2FE-4E8D-84FB-657049B41931}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Ai 변화</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -85,6 +85,14 @@
   </si>
   <si>
     <t>파이썬 설치시 체크하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[선생님 구글드라이브 공유 링크]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1ew-PlWEsXgxY8T_WAjzYSrRmKvRQZhLE?usp=drive_link</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -92,7 +100,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,6 +111,15 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -126,18 +143,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -449,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C522516C-CF92-4DAF-812F-1C05FE71279D}">
-  <dimension ref="B2:C22"/>
+  <dimension ref="B2:C25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.3">
@@ -518,10 +542,23 @@
         <v>9</v>
       </c>
     </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B25" r:id="rId1" xr:uid="{EE59AE16-D019-4207-9329-14D809099669}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
